--- a/data/b2_indio/B2 Índio 06-2026.xlsx
+++ b/data/b2_indio/B2 Índio 06-2026.xlsx
@@ -4793,38 +4793,38 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>3337.95</v>
+        <v>52073.72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>51317.19</v>
+        <v>1417.78</v>
       </c>
     </row>
     <row r="4">
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>3292.89</v>
+        <v>3013.49</v>
       </c>
     </row>
     <row r="5">
@@ -4851,16 +4851,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>1888.62</v>
+        <v>1855.52</v>
       </c>
     </row>
     <row r="6">
@@ -4883,74 +4883,74 @@
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>2037.5</v>
+        <v>2036.33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46184</v>
+        <v>46186</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>711.33</v>
+        <v>3282.17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46185</v>
+        <v>46187</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1951.19</v>
+        <v>3229.95</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>3128.82</v>
+        <v>9584.549999999999</v>
       </c>
     </row>
     <row r="11">
@@ -4959,88 +4959,88 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>9121.41</v>
+        <v>1545.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1547.65</v>
+        <v>1176.74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46189</v>
+        <v>46193</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>1718.62</v>
+        <v>18308.98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>18209.68</v>
+        <v>3109.48</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46194</v>
+        <v>46196</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>2762.01</v>
+        <v>1631.35</v>
       </c>
     </row>
     <row r="16">
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3001.89</v>
+        <v>3138</v>
       </c>
     </row>
     <row r="17">
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>827.79</v>
+        <v>904.49</v>
       </c>
     </row>
   </sheetData>
